--- a/Output/PowerPoint_Figures/Fig_S1/Fig_S1a_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_S1/Fig_S1a_data.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,120 +418,120 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="n">
+      <c r="B1" t="n">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="C1" t="n">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" t="n">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" t="n">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" t="n">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" t="n">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" t="n">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" t="n">
         <v>19</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" t="n">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" t="n">
         <v>24</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="L1" t="n">
         <v>27</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="M1" t="n">
         <v>30</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="N1" t="n">
         <v>32</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="O1" t="n">
         <v>35</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="P1" t="n">
         <v>38</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="Q1" t="n">
         <v>40</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="R1" t="n">
         <v>43</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="S1" t="n">
         <v>45</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="T1" t="n">
         <v>48</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="U1" t="n">
         <v>51</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="V1" t="n">
         <v>53</v>
       </c>
-      <c r="W1" s="1" t="n">
+      <c r="W1" t="n">
         <v>56</v>
       </c>
-      <c r="X1" s="1" t="n">
+      <c r="X1" t="n">
         <v>59</v>
       </c>
-      <c r="Y1" s="1" t="n">
+      <c r="Y1" t="n">
         <v>61</v>
       </c>
-      <c r="Z1" s="1" t="n">
+      <c r="Z1" t="n">
         <v>64</v>
       </c>
-      <c r="AA1" s="1" t="n">
+      <c r="AA1" t="n">
         <v>66</v>
       </c>
-      <c r="AB1" s="1" t="n">
+      <c r="AB1" t="n">
         <v>69</v>
       </c>
-      <c r="AC1" s="1" t="n">
+      <c r="AC1" t="n">
         <v>72</v>
       </c>
-      <c r="AD1" s="1" t="n">
+      <c r="AD1" t="n">
         <v>74</v>
       </c>
-      <c r="AE1" s="1" t="n">
+      <c r="AE1" t="n">
         <v>77</v>
       </c>
-      <c r="AF1" s="1" t="n">
+      <c r="AF1" t="n">
         <v>80</v>
       </c>
-      <c r="AG1" s="1" t="n">
+      <c r="AG1" t="n">
         <v>82</v>
       </c>
-      <c r="AH1" s="1" t="n">
+      <c r="AH1" t="n">
         <v>85</v>
       </c>
-      <c r="AI1" s="1" t="n">
+      <c r="AI1" t="n">
         <v>88</v>
       </c>
-      <c r="AJ1" s="1" t="n">
+      <c r="AJ1" t="n">
         <v>90</v>
       </c>
-      <c r="AK1" s="1" t="n">
+      <c r="AK1" t="n">
         <v>93</v>
       </c>
-      <c r="AL1" s="1" t="n">
+      <c r="AL1" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -579,7 +567,7 @@
         <v>2.708816430394807</v>
       </c>
       <c r="L2" t="n">
-        <v>1.911975597368205</v>
+        <v>1.911975597368206</v>
       </c>
       <c r="M2" t="n">
         <v>3.362733495219779</v>
@@ -612,7 +600,7 @@
         <v>1.849137978442418</v>
       </c>
       <c r="W2" t="n">
-        <v>1.881415963416188</v>
+        <v>1.881415963416187</v>
       </c>
       <c r="X2" t="n">
         <v>1.819597947381446</v>
@@ -630,7 +618,7 @@
         <v>2.370751025767911</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.303714491125365</v>
+        <v>2.303714491125366</v>
       </c>
       <c r="AD2" t="n">
         <v>2.507642807604928</v>
@@ -659,7 +647,7 @@
       <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
@@ -777,7 +765,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -895,7 +883,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -1003,7 +991,7 @@
         <v>4.354961554462345</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.21320209735558</v>
+        <v>4.213202097355579</v>
       </c>
       <c r="AK5" t="n">
         <v>4.867837143412349</v>
@@ -1013,7 +1001,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1131,7 +1119,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1245,7 +1233,7 @@
       <c r="AL7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
@@ -1260,7 +1248,7 @@
         <v>1.152308019878707</v>
       </c>
       <c r="E8" t="n">
-        <v>2.923730291127008</v>
+        <v>2.923730291127007</v>
       </c>
       <c r="F8" t="n">
         <v>1.398451284806108</v>
@@ -1329,7 +1317,7 @@
         <v>3.166884836954043</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.925027265409151</v>
+        <v>3.92502726540915</v>
       </c>
       <c r="AC8" t="n">
         <v>3.237745100498424</v>
@@ -1361,7 +1349,7 @@
       <c r="AL8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -1479,7 +1467,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1593,7 +1581,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
@@ -1709,7 +1697,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
@@ -1825,7 +1813,7 @@
       <c r="AL12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -1841,7 +1829,7 @@
         <v>0.8516279512954595</v>
       </c>
       <c r="F13" t="n">
-        <v>1.802910149051665</v>
+        <v>1.802910149051666</v>
       </c>
       <c r="G13" t="n">
         <v>1.001742280821882</v>
@@ -1941,7 +1929,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>0.5.1</t>
         </is>
@@ -2059,7 +2047,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>0.5.2</t>
         </is>
@@ -2086,7 +2074,7 @@
         <v>1.833713119649592</v>
       </c>
       <c r="I15" t="n">
-        <v>1.959576259602925</v>
+        <v>1.959576259602926</v>
       </c>
       <c r="J15" t="n">
         <v>4.05054490199086</v>
@@ -2177,7 +2165,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>0.5.3</t>
         </is>
@@ -2216,7 +2204,7 @@
         <v>2.761551354618279</v>
       </c>
       <c r="M16" t="n">
-        <v>2.102379138932477</v>
+        <v>2.102379138932478</v>
       </c>
       <c r="N16" t="n">
         <v>2.172562914775946</v>
@@ -2295,7 +2283,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
@@ -2349,7 +2337,7 @@
         <v>1.403957225278235</v>
       </c>
       <c r="R17" t="n">
-        <v>3.638946169393592</v>
+        <v>3.638946169393591</v>
       </c>
       <c r="S17" t="n">
         <v>1.69805393423209</v>
@@ -2413,7 +2401,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>0.25.1</t>
         </is>
@@ -2488,7 +2476,7 @@
         <v>3.799341018554911</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.689295573206897</v>
+        <v>3.689295573206898</v>
       </c>
       <c r="Z18" t="n">
         <v>3.789968741699998</v>
@@ -2512,7 +2500,7 @@
         <v>4.12857409139496</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.9733108975376</v>
+        <v>3.973310897537599</v>
       </c>
       <c r="AH18" t="n">
         <v>3.459042900284006</v>
@@ -2531,7 +2519,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>0.25.2</t>
         </is>
@@ -2649,7 +2637,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>0.125</t>
         </is>
@@ -2742,7 +2730,7 @@
         <v>1.349183525913935</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.610634027728617</v>
+        <v>3.610634027728618</v>
       </c>
       <c r="AF20" t="n">
         <v>1.570505169200817</v>
@@ -2767,7 +2755,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>0.125.1</t>
         </is>
@@ -2885,7 +2873,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>0.125.2</t>
         </is>
@@ -2990,7 +2978,7 @@
         <v>1.527883903882848</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.004300931053573</v>
+        <v>2.004300931053574</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.544043890985847</v>
@@ -3003,7 +2991,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>0.125.3</t>
         </is>
@@ -3121,7 +3109,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>0.062</t>
         </is>
@@ -3239,7 +3227,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>0.062.1</t>
         </is>
@@ -3357,7 +3345,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>0.062.2</t>
         </is>
@@ -3396,7 +3384,7 @@
         <v>2.126567136179596</v>
       </c>
       <c r="M26" t="n">
-        <v>2.237201471154356</v>
+        <v>2.237201471154355</v>
       </c>
       <c r="N26" t="n">
         <v>2.752744160665622</v>
@@ -3432,7 +3420,7 @@
         <v>2.355074833920097</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.148369837282789</v>
+        <v>2.14836983728279</v>
       </c>
       <c r="Z26" t="n">
         <v>2.02388703278152</v>
@@ -3462,7 +3450,7 @@
         <v>1.891416655315867</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.912200474450864</v>
+        <v>1.912200474450863</v>
       </c>
       <c r="AJ26" t="n">
         <v>2.563472419408959</v>
@@ -3475,7 +3463,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>0.062.3</t>
         </is>
@@ -3499,7 +3487,7 @@
         <v>2.523970395895351</v>
       </c>
       <c r="H27" t="n">
-        <v>2.141377153270976</v>
+        <v>2.141377153270975</v>
       </c>
       <c r="I27" t="n">
         <v>2.325435577688209</v>
@@ -3544,7 +3532,7 @@
         <v>2.940672836148978</v>
       </c>
       <c r="W27" t="n">
-        <v>2.40805294646226</v>
+        <v>2.408052946462259</v>
       </c>
       <c r="X27" t="n">
         <v>2.869792019890038</v>
@@ -3607,29 +3595,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Drug</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\Heatmaps\Vandetanib (G11)\O2_std.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/Heatmaps/Vandetanib (G11)/O2_std.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
